--- a/new/260830.xlsx
+++ b/new/260830.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDDE22DC-6C2B-4FD4-8F95-5D2079281519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE89E02F-C377-4576-88A5-108C0762E29B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="1520" windowWidth="15030" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8470" yWindow="2810" windowWidth="15030" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
-    <sheet name="SheetX" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
+    <sheet name="SheetX" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Trotz der Umsetzung von Industrie 4.0 an unseren Standorten ist die Anzahl der Belegschaft nicht zurückgegangen.
 Es hat sich aber ein Wandel in den Arbeitsplätzen ergeben, wie ich vorhin schon ausführte.
@@ -212,60 +213,6 @@
 Scholz: Wer realistisch ist, kann immer nur sagen: Wir können das schaffen.
 Aber die Bürgerinnen und Bürger haben einen großen Beitrag dazu geleistet, dass zusammen mit einer sehr engagierten Verwaltung wir ganz schön weit gekommen sind und uns jetzt an die nächsten Aufgaben machen.
 Detjen: Herr Bürgermeister, vielen Dank.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Denn eines muss man sehen: Auch der Rechtsextremismus ist nicht nur auf Deutschland beschränkt.
-Auch hier gibt es immer wieder Kontakte in das Ausland.
-Sei es allein, was die Beschaffung bestimmter pyrotechnischer Gegenstände anbelangt.
-Sei es als Rückzugsgebiete oder Vernetzung mit anderen ausländischen rechtsterroristischen oder rechtsextremistischen Strukturen.
-Wir haben ein Ansprechpartner-Netzwerk entwickelt.
-Wir versuchen auch, dieses noch weiter zu entwickeln, indem wir die Länderstaatsanwaltschaften noch enger an uns heranbinden.
-Und insoweit berichten uns die Länder sehr frühzeitig.
-Wir berichten den Ländern aufgrund unserer Erkenntnisse.
-Und ich glaube, das ist auch das Entscheidende.
-Geuther: Es wurde einzelnen Ländern – gerade auch im Osten der Republik – vorgeworfen, eine Tat später als rechtsextremistisch einzuordnen als andere – vorsichtig gesagt.
-Stimmt das?
-Und wenn ja, stimmt das immer noch?
-Frank: Um hier eine Sensibilisierung auch bei jedem zu erreichen, haben wir, hat die Bundesanwaltschaft, in Zusammenarbeit aber auch mit den Generalstaatsanwaltschaften der Länder verschiedene Instrumentarien entwickelt.
-Eines ist zum Beispiel – auch, wenn das vielleicht banal klingen mag – die Entwicklung eines Formblattes, wie man frühzeitig rechtsextremistische Straftaten erkennen kann.
-Denn vielfach ist ein erster Kontakt mit rechtsextremistischen Straftaten nicht immer dann gegeben, wenn Volksverhetzungen begangen wurden, der Hitler-Gruß gezeigt wird, wenn Hakenkreuze an die Wand gemalt werden.
-Häufig sind es Straftaten der Allgemeinkriminalität.
-Es sind Körperverletzungshandlungen.
-Und hier muss jeder Staatsanwalt frühzeitig wissen – nicht nur der Staatsanwalt, der sich in einer Spezialabteilung befindet –, muss sich jeder Staatsanwalt frühzeitig bewusst werden: Gibt es hier Erkenntnisse, die darauf hindeuten, dass es sich um einen rechtsextremistischen Hintergrund handelt?
-Und insoweit haben wir versucht, jeden Staatsanwalt und im Übrigen auch versucht, jeden Vollzugsbeamten – denn man muss auch im Strafvollzug erkennen: Jemand, der wegen eines Diebstahls, eines Ladendiebstahls sitzt, auch der kann einen rechtsextremistischen Hintergrund haben – frühzeitig diese Strukturen zu erkennen, um sie dann den zuständigen Behörden zu melden, damit sich daraus nichts verfestigt.
-Geuther: Es gab im vergangenen Jahr fast 1.500 politisch rechts motivierte Gewalttaten und darunter eine bisher nie gehabte Zahl von Angriffen auf Flüchtlingsunterkünfte.
-Wie gehen Sie als Generalbundesanwalt damit um?
-Frank: Für die Beobachtung von rechtsextremistischen Straftaten gibt es im Bundesamt für Verfassungsschutz das gemeinsame Extremismus- und Terrorismusabwehrzentrum rechts, in dem auch wir – die Bundesanwaltschaft – vertreten sind.
-In diesem Zentrum, das eine Plattform darstellt, in dem Polizeibehörden, Dienste, Nachrichtendienste, aber auch die Staatsanwaltschaft vertreten ist, werden solche Vorfälle gemeinsam bewertet.
-Wir, die Bundesanwaltschaft, schauen uns diese schwerwiegenden Straftaten, wenn sie ein bestimmtes Ausmaß erreicht haben, immer wieder an, um dort auch herauszufinden, ob sich Strukturen bilden.
-Das ist eine der Konsequenzen auch der Ergebnisse aus der Aufarbeitung NSU, dass wir verschiedene Strukturverfahren angelegt haben, um frühzeitig herauszufinden: Welche Entwicklungen spielen sich in bestimmten Bereichen ab?
-Wir haben – gerade, was die Anschläge auf die Flüchtlingsheime im letzten Jahr anbelangt – Strukturen, Verfahren geführt, um festzustellen: Gibt es Vernetzungen?
-Sind das nur Taten von Einzelpersonen oder von lokalen kleineren Gruppierungen?
-Oder hat sich da eine größere Vernetzungsstruktur gebildet?
-Findet da vielleicht eine Steuerung aus einem etwas größeren Ganzen statt?
-Wir haben auch im Blick, zusammen mit den Polizei- und den Verfassungsschutzbehörden: rechtsextremistische Musikgruppen.
-Wir haben im Blick besonders: rechtsextremistische Gefährder.
-Wir stehen insoweit in einem engen Kontakt und Austausch mit dem Bundeskriminalamt.
-Wir kriegen in regelmäßigen Abständen alle Gefährder aus dem rechtsextremistischen Bereich gemeldet, die wir dann wiederum mit unseren Erkenntnissen versuchen abzuklären.
-Nur, wenn man versucht, das Phänomen Bereich Rechtsextremismus ganzheitlich zu betrachten und unter allen möglichen Aspekten und Blickwinkeln auch zu durchleuchten, dann lässt sich frühzeitig verhindern, dass sich wieder eine neue Struktur NSU bildet.
-Das ist für uns sehr wichtig.
-Geuther: Jetzt haben wir über Rechtsextremismus gesprochen, vorher über den Islamismus, über eine Amok-Tat.
-Gleichzeitig waren laut Verfassungsschutzbericht auch Linksextremisten im vergangenen Jahr deutlich gewalttätiger als zuvor.
-Und man könnte auch weitergehen.
-Die Verrohung steigt offenbar insgesamt.
-Nicht nur in der Sprache im Internet, auch im öffentlichen Dienst, im Arbeitsamt oder in der Ausländerbehörde werden Mitarbeiter öfter angegriffen.
-Was kann Recht da überhaupt leisten?
-Frank: Es ist seit längerer Zeit zu erkennen, dass die Gewaltbereitschaft in Deutschland zugenommen hat.
-Und so, wie Sie es beschrieben haben, es beginnt zunächst einmal mit einer Verrohung der Sprache.
-Und es führt dann zu einer Verrohung auch in der körperlichen Auseinandersetzung.
-Seit Jahren steigt der Anteil von Gewaltstraftaten.
-Und auch, wenn man sich die Entwicklung innerhalb der Gewaltstraftaten anschaut, so findet man immer wieder einen Anstieg auch der Vehemenz von Gewalt.
-Recht – und das ist das Entscheidende und Wichtige von Recht – Recht muss immer durchgesetzt werden.
-Recht muss insoweit standhaft bleiben, denn sonst verliert das Recht seine Achtung.
-Wir haben in Deutschland Werte letztendlich immer durch Rechtsnormen versucht auch abzusichern und Werteentfaltung durch das Schaffen von Recht einen Rahmen zu geben.
-Und nur, wenn wir diesen Rechtsrahmen auch konsequent verteidigen – und dazu gehört eine konsequente Strafverfolgung – nur, wenn wir diesen Rechtsrahmen verteidigen, dann haben wir eine Chance, dass das Recht und damit auch die Werte erhalten bleiben.
-Geuther: Herr Generalbundesanwalt, vielen Dank für das Gespräch</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -462,6 +409,54 @@
 Aber ich bin von den Kölnern ganz und gar überzeugt, ich bin sogar stolz darauf,  und ein hohes ehrenamtliches Engagement zeigen auf Dauer bei der Unterbringung von Flüchtlingen, also eine echte Willkommenskultur.
 Küpper: sie aus der Türkei gesteuert wird.
 Die DITIB ist im Stadtbild ja auch sehr präsent durch diese große Moschee, den großen Moscheebau, der allerdings seit Jahren auf seine Fertigstellung wartet.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Und hier muss jeder Staatsanwalt frühzeitig wissen – nicht nur der Staatsanwalt, der sich in einer Spezialabteilung befindet –, muss sich jeder Staatsanwalt frühzeitig bewusst werden: Gibt es hier Erkenntnisse, die darauf hindeuten, dass es sich um einen rechtsextremistischen Hintergrund handelt?
+Und insoweit haben wir versucht, jeden Staatsanwalt und im Übrigen auch versucht, jeden Vollzugsbeamten – denn man muss auch im Strafvollzug erkennen: Jemand, der wegen eines Diebstahls, eines Ladendiebstahls sitzt, auch der kann einen rechtsextremistischen Hintergrund haben – frühzeitig diese Strukturen zu erkennen, um sie dann den zuständigen Behörden zu melden, damit sich daraus nichts verfestigt.
+Geuther: Es gab im vergangenen Jahr fast 1.500 politisch rechts motivierte Gewalttaten und darunter eine bisher nie gehabte Zahl von Angriffen auf Flüchtlingsunterkünfte.
+Wie gehen Sie als Generalbundesanwalt damit um?
+Frank: Für die Beobachtung von rechtsextremistischen Straftaten gibt es im Bundesamt für Verfassungsschutz das gemeinsame Extremismus- und Terrorismusabwehrzentrum rechts, in dem auch wir – die Bundesanwaltschaft – vertreten sind.
+In diesem Zentrum, das eine Plattform darstellt, in dem Polizeibehörden, Dienste, Nachrichtendienste, aber auch die Staatsanwaltschaft vertreten ist, werden solche Vorfälle gemeinsam bewertet.
+Wir, die Bundesanwaltschaft, schauen uns diese schwerwiegenden Straftaten, wenn sie ein bestimmtes Ausmaß erreicht haben, immer wieder an, um dort auch herauszufinden, ob sich Strukturen bilden.
+Das ist eine der Konsequenzen auch der Ergebnisse aus der Aufarbeitung NSU, dass wir verschiedene Strukturverfahren angelegt haben, um frühzeitig herauszufinden: Welche Entwicklungen spielen sich in bestimmten Bereichen ab?
+Wir haben – gerade, was die Anschläge auf die Flüchtlingsheime im letzten Jahr anbelangt – Strukturen, Verfahren geführt, um festzustellen: Gibt es Vernetzungen?
+Sind das nur Taten von Einzelpersonen oder von lokalen kleineren Gruppierungen?
+Oder hat sich da eine größere Vernetzungsstruktur gebildet?
+Findet da vielleicht eine Steuerung aus einem etwas größeren Ganzen statt?
+Wir haben auch im Blick, zusammen mit den Polizei- und den Verfassungsschutzbehörden: rechtsextremistische Musikgruppen.
+Wir haben im Blick besonders: rechtsextremistische Gefährder.
+Wir stehen insoweit in einem engen Kontakt und Austausch mit dem Bundeskriminalamt.
+Wir kriegen in regelmäßigen Abständen alle Gefährder aus dem rechtsextremistischen Bereich gemeldet, die wir dann wiederum mit unseren Erkenntnissen versuchen abzuklären.
+Nur, wenn man versucht, das Phänomen Bereich Rechtsextremismus ganzheitlich zu betrachten und unter allen möglichen Aspekten und Blickwinkeln auch zu durchleuchten, dann lässt sich frühzeitig verhindern, dass sich wieder eine neue Struktur NSU bildet.
+Das ist für uns sehr wichtig.
+Geuther: Jetzt haben wir über Rechtsextremismus gesprochen, vorher über den Islamismus, über eine Amok-Tat.
+Gleichzeitig waren laut Verfassungsschutzbericht auch Linksextremisten im vergangenen Jahr deutlich gewalttätiger als zuvor.
+Und man könnte auch weitergehen.
+Die Verrohung steigt offenbar insgesamt.
+Nicht nur in der Sprache im Internet, auch im öffentlichen Dienst, im Arbeitsamt oder in der Ausländerbehörde werden Mitarbeiter öfter angegriffen.
+Was kann Recht da überhaupt leisten?
+Frank: Es ist seit längerer Zeit zu erkennen, dass die Gewaltbereitschaft in Deutschland zugenommen hat.
+Und so, wie Sie es beschrieben haben, es beginnt zunächst einmal mit einer Verrohung der Sprache.
+Und es führt dann zu einer Verrohung auch in der körperlichen Auseinandersetzung.
+Seit Jahren steigt der Anteil von Gewaltstraftaten.
+Und auch, wenn man sich die Entwicklung innerhalb der Gewaltstraftaten anschaut, so findet man immer wieder einen Anstieg auch der Vehemenz von Gewalt.
+Recht – und das ist das Entscheidende und Wichtige von Recht – Recht muss immer durchgesetzt werden.
+Recht muss insoweit standhaft bleiben, denn sonst verliert das Recht seine Achtung.
+Wir haben in Deutschland Werte letztendlich immer durch Rechtsnormen versucht auch abzusichern und Werteentfaltung durch das Schaffen von Recht einen Rahmen zu geben.
+Und nur, wenn wir diesen Rechtsrahmen auch konsequent verteidigen – und dazu gehört eine konsequente Strafverfolgung – nur, wenn wir diesen Rechtsrahmen verteidigen, dann haben wir eine Chance, dass das Recht und damit auch die Werte erhalten bleiben.
+Geuther: Herr Generalbundesanwalt, vielen Dank für das Gespräch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>indem wir die Länderstaatsanwaltschaften noch enger an uns heranbinden.
+Und insoweit berichten uns die Länder sehr frühzeitig.
+Wir berichten den Ländern aufgrund unserer Erkenntnisse.
+Frank: Um hier eine Sensibilisierung auch bei jedem zu erreichen, haben wir.
+Eines ist zum Beispiel – auch, wenn das vielleicht banal klingen mag – die Entwicklung eines Formblattes, wie man frühzeitig rechtsextremistische Straftaten erkennen kann.
+wenn Volksverhetzungen begangen wurden, der Hitler-Gruß gezeigt wird, wenn Hakenkreuze an die Wand gemalt werden.
+Häufig sind es Straftaten der Allgemeinkriminalität.
+Es sind Körperverletzungshandlungen.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -798,7 +793,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="364" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -808,6 +803,25 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57D4BF05-4855-4209-A1CA-54B8560163E1}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="29.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="350" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -821,24 +835,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>2</v>
@@ -850,7 +864,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/new/260830.xlsx
+++ b/new/260830.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE89E02F-C377-4576-88A5-108C0762E29B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6A0B4FF-5093-4775-9A1B-9D408ED966B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8470" yWindow="2810" windowWidth="15030" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8400" yWindow="4110" windowWidth="15030" windowHeight="11170" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
-    <sheet name="SheetX" sheetId="1" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="4" r:id="rId3"/>
+    <sheet name="SheetX" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Trotz der Umsetzung von Industrie 4.0 an unseren Standorten ist die Anzahl der Belegschaft nicht zurückgegangen.
 Es hat sich aber ein Wandel in den Arbeitsplätzen ergeben, wie ich vorhin schon ausführte.
@@ -150,69 +151,6 @@
 In dem Interview hier war es deshalb gut, weil wir fast nur über Sachfragen geredet haben, sonst hätten wir ausschließlich über Personen geredet – ist meine Vermutung.
 Und ich glaube, dass es klug ist, erst mal zu sagen, was man will und dann am Ende auch eine Person – natürlich brauchen wir die – zu bestimmen und es nicht umgekehrt zu machen.
 Und dann bin ich ein bisschen lästerlich und sage: Solange die Kanzlerin noch nicht einmal gesagt hat, ob sie noch mal kandidiert, müssen wir noch keinen Kandidaten nennen</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Detjen: Das bezieht sich jetzt auf Koalitionen auf Bundesebene, was Regierung angeht.
-Vor der Bundestagswahl, vor der Bildung einer Bundesregierung steht die Wahl eines Bundespräsidenten, eine sozusagen rot-rot-grüne Koalition in der Bundesversammlung.
-Ist das für Sie erstrebenswert?
-Scholz: Ich wünsche mir, dass jemand Präsident oder Präsidentin wird, von dem die Bürgerinnen und Bürger sagen: Das ist ein guter Präsident, das ist eine gute Präsidentin.
-Da geht es nicht zu allererst um Parteipolitik, sondern darum, dass das Land zusammengehalten wird.
-Und das sollte auch im Vordergrund der Bemühungen stehen.
-Ich fände es auch sehr gut möglich, dass sich Parteien der jetzigen Regierung auf einen gemeinsamen Kandidaten verständigen, den auch die Grünen zum Beispiel und andere gut finden.
-Detjen: Herr Scholz, jetzt beginnt für die Parteien, zunächst mal als Vorbereitung auf die Wahl, die Aufstellung der Kandidatenlisten – das betrifft auch die SPD in Hamburg natürlich.
-Können Sie gewährleisten, dass die SPD in Hamburg keine Kandidatinnen oder Kandidaten aufstellt, die dann danach mit gefälschten Lebensläufen den Bürgern etwas vormachen?
-Scholz: Das glaube ich schon.
-Detjen: Das war in Nordrhein-Westfalen offenbar nicht so einfach.
-Was ist da schiefgelaufen?
-Scholz: Weiß ich nicht.
-Ich kenne mich vor Ort nicht genug aus.
-Ich glaube, dass alle sehr betrübt darüber sind, dass es so ist.
-Und das muss jetzt auch schnell in Ordnung gebracht werden.
-Detjen: Zu den Befunden in dieser Affäre um die SPD-Bundestagsabgeordnete Petra Hinz gehört ja auch das Bild, dass da eine SPD-Abgeordnete war, die eigentlich niemand richtig kannte.
-Der Vorsitzende des SPD-Unterbezirks Essen, der nordrhein-westfälische Justizminister Kutschaty sagt, es habe eigentlich gar keine persönlichen Beziehungen zu dieser Abgeordneten gegeben.
-Schlagen sich da ein paar Genossen jetzt im Nachhinein in die Büsche?
-Oder wirft diese Affäre ein Schlaglicht auf eine für die Politik vielleicht typische Verkümmerung von menschlichen Beziehungen?
-Scholz: Letzteres ganz bestimmt nicht.
-Wie es dazu gekommen ist, dass das niemand bemerkt hat, auch die ja immer sehr kritische Öffentlichkeit und Presse nicht.
-Das kann ich mir auch nicht so richtig erklären.
-Auf alle Fälle, wenn alles zu Ende ist, wird es sicherlich ein gutes Buch über das Thema geben und dann werden wir mehr lernen.
-Detjen: Sie haben vor ein paar Wochen, Herr Scholz, ein Papier geschrieben, das trug die Überschrift: Die Partei der schlechten Laune.
-Das bezog sich nicht auf die SPD, richtig?
-Scholz: Klar, das bezog sich auf die AfD.  Dafür sorgen, dass es eine gute Zukunft gibt Detjen: Warum ist die für Sie die  Partei der schlechten Laune ?
-Scholz: Weil es ja keine konkreten Vorstellungen gibt darüber, wie es weitergehen soll mit unserem Land, sondern vor allem der Eindruck erweckt wird, alles läuft schief und es geht in die falsche Richtung.
-Ich glaube, dass es immer wichtig ist, dass man Vorstellungen dafür hat, wie man mit demokratischer Politik unser Land besser machen kann und dass man sich auch auf ganz, ganz, ganz konkrete Fragen beziehen muss.
-Was machen wir mit unseren öffentlichen Haushalten?
-Wie statten wir die Bundeswehr und unsere Polizei gut aus?
-Was machen wir, um die Bildung zu verbessern an den Schulen?
-Wie setzen wir Forschung und Universitäten auf die richtige Spur?
-Also immer ganz konkrete Politik, bei der es darum geht: Wie können wir dafür sorgen, dass es eine gute Zukunft gibt.
-Und über sowas muss man diskutieren.
-Und ich glaube, dass das auch der richtige Umgang ist in der Sache.
-Detjen: Dann werfen wir am Ende des Gesprächs nochmal den Blick auf das konkrete Thema, das uns alle, das das Land im vergangenen Jahr am meisten beschäftigt hat.
-Vor einem Jahr um diese Zeit schwante den meisten, dass mit der Flüchtlingsbewegung eine riesige Aufgabe, eine Generationenaufgabe auf Bund, Länder, Kommunen zukommen.
-Wenn Sie jetzt Hamburg anschauen, was sich in diesem Jahr getan hat, ist das für Sie ein Anlass, gut gelaunt auf die Entwicklung zu schauen oder eher schlecht gelaunt?
-Scholz: Was letztes Jahr stattfand, war eine unglaubliche Herausforderung.
-Und – das, glaube ich, muss man auch ganz offen sagen – in Deutschland war nicht überall klar, wer wann wo ist und wer wohin kommen soll und wer wo aufgenommen wird.
-Mittlerweile sind viele Institutionen, insbesondere auch das Bundesamt für Migration und Flüchtlinge, massiv ausgebaut worden.
-Dieser Ausbauprozess ist noch nicht beendet, das muss nun bald erfolgen.
-Und wir müssen mit den gesetzlichen Änderungen, die wir ergriffen haben, mit all den Maßnahmen, die wir getroffen haben, vorbereitet sein auf solche Entwicklungen.
-Das muss das Ergebnis des letzten Jahres sein.
-Denn wir können ja nicht sicher sein, dass nicht irgendwann mal wieder eine große Zahl von Flüchtlingen kommt.
-Jetzt sieht es ein wenig danach aus, dass es weniger werden und wir uns jetzt auf die Aufgabe konzentrieren können, diejenigen, die länger bleiben werden, zu integrieren.
-Detjen: Nochmal der Blick konkret auf Hamburg.
-Was haben Sie geschafft in diesem Jahr?
-Scholz: Wir haben Tausende von Unterkunftsplätzen geschaffen, was nicht ganz einfach ist in einer Stadt, die sehr bebaut ist und relativ mehr Flüchtlinge aufnimmt als andere, weil bei der Verteilung der Flüchtlinge in Deutschland Bevölkerungszahl und Wirtschaftskraft eine Rolle spielen und nicht die Frage 'Wieviel Platz hat man so?
-'.
-Das haben wir aber gemeistert und haben uns auch über viele Standorte verständigt, haben mit vielen Bürgerinnen und Bürgern gesprochenen, verhandelt, haben unglaublich viel Unterstützung bekommen von denjenigen, die in den Flüchtlingsunterkünften helfen.
-Und wir haben sofort dafür gesorgt, dass mehr Angebote gemacht werden bei Krippen und Kitas, bei den Schulen, haben zusätzliche Lehrerinnen und Lehrer eingestellt, damit es ohne Beeinträchtigung des bisherigen Betriebs zu einer schnellen Integration der jungen Leute kommt.
-Wir haben uns sofort darauf konzentriert, diejenigen, die in dem Alter sind, in dem man zur Berufsschule geht, dort auszubilden, auch mit einer Berufsorientierung zu versehen.
-Und wir haben Angebote entwickelt, die für diejenigen, die erwachsen sind, eine Arbeitsmarktintegration in den Blick nehmen.
-Detjen: Und vieles ist noch zu tun.
-Würden Sie Ihren Bürgerinnen und Bürgern in Hamburg sagen:  Wir schaffen das ?
-Scholz: Wer realistisch ist, kann immer nur sagen: Wir können das schaffen.
-Aber die Bürgerinnen und Bürger haben einen großen Beitrag dazu geleistet, dass zusammen mit einer sehr engagierten Verwaltung wir ganz schön weit gekommen sind und uns jetzt an die nächsten Aufgaben machen.
-Detjen: Herr Bürgermeister, vielen Dank.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -457,6 +395,63 @@
 wenn Volksverhetzungen begangen wurden, der Hitler-Gruß gezeigt wird, wenn Hakenkreuze an die Wand gemalt werden.
 Häufig sind es Straftaten der Allgemeinkriminalität.
 Es sind Körperverletzungshandlungen.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>es habe eigentlich gar keine persönlichen Beziehungen zu dieser Abgeordneten gegeben.
+Schlagen sich da ein paar Genossen jetzt im Nachhinein in die Büsche?
+Oder wirft diese Affäre ein Schlaglicht auf eine für die Politik vielleicht typische Verkümmerung von menschlichen Beziehungen?
+Scholz: Letzteres ganz bestimmt nicht.
+Wie es dazu gekommen ist, dass das niemand bemerkt hat, auch die ja immer sehr kritische Öffentlichkeit und Presse nicht.
+Das kann ich mir auch nicht so richtig erklären.
+Auf alle Fälle, wenn alles zu Ende ist, wird es sicherlich ein gutes Buch über das Thema geben und dann werden wir mehr lernen.
+Detjen: Sie haben vor ein paar Wochen, Herr Scholz, ein Papier geschrieben, das trug die Überschrift: Die Partei der schlechten Laune.
+Das bezog sich nicht auf die SPD, richtig?
+Scholz: Klar, das bezog sich auf die AfD.  Dafür sorgen, dass es eine gute Zukunft gibt Detjen: Warum ist die für Sie die  Partei der schlechten Laune ?
+Scholz: Weil es ja keine konkreten Vorstellungen gibt darüber, wie es weitergehen soll mit unserem Land, sondern vor allem der Eindruck erweckt wird, alles läuft schief und es geht in die falsche Richtung.
+Ich glaube, dass es immer wichtig ist, dass man Vorstellungen dafür hat, wie man mit demokratischer Politik unser Land besser machen kann und dass man sich auch auf ganz, ganz, ganz konkrete Fragen beziehen muss.
+Was machen wir mit unseren öffentlichen Haushalten?
+Wie statten wir die Bundeswehr und unsere Polizei gut aus?
+Was machen wir, um die Bildung zu verbessern an den Schulen?
+Wie setzen wir Forschung und Universitäten auf die richtige Spur?
+Also immer ganz konkrete Politik, bei der es darum geht: Wie können wir dafür sorgen, dass es eine gute Zukunft gibt.
+Und über sowas muss man diskutieren.
+Und ich glaube, dass das auch der richtige Umgang ist in der Sache.
+Detjen: Dann werfen wir am Ende des Gesprächs nochmal den Blick auf das konkrete Thema, das uns alle, das das Land im vergangenen Jahr am meisten beschäftigt hat.
+Vor einem Jahr um diese Zeit schwante den meisten, dass mit der Flüchtlingsbewegung eine riesige Aufgabe, eine Generationenaufgabe auf Bund, Länder, Kommunen zukommen.
+Wenn Sie jetzt Hamburg anschauen, was sich in diesem Jahr getan hat, ist das für Sie ein Anlass, gut gelaunt auf die Entwicklung zu schauen oder eher schlecht gelaunt?
+Scholz: Was letztes Jahr stattfand, war eine unglaubliche Herausforderung.
+Und – das, glaube ich, muss man auch ganz offen sagen – in Deutschland war nicht überall klar, wer wann wo ist und wer wohin kommen soll und wer wo aufgenommen wird.
+Mittlerweile sind viele Institutionen, insbesondere auch das Bundesamt für Migration und Flüchtlinge, massiv ausgebaut worden.
+Dieser Ausbauprozess ist noch nicht beendet, das muss nun bald erfolgen.
+Und wir müssen mit den gesetzlichen Änderungen, die wir ergriffen haben, mit all den Maßnahmen, die wir getroffen haben, vorbereitet sein auf solche Entwicklungen.
+Das muss das Ergebnis des letzten Jahres sein.
+Denn wir können ja nicht sicher sein, dass nicht irgendwann mal wieder eine große Zahl von Flüchtlingen kommt.
+Jetzt sieht es ein wenig danach aus, dass es weniger werden und wir uns jetzt auf die Aufgabe konzentrieren können, diejenigen, die länger bleiben werden, zu integrieren.
+Detjen: Nochmal der Blick konkret auf Hamburg.
+Was haben Sie geschafft in diesem Jahr?
+Scholz: Wir haben Tausende von Unterkunftsplätzen geschaffen, was nicht ganz einfach ist in einer Stadt, die sehr bebaut ist und relativ mehr Flüchtlinge aufnimmt als andere, weil bei der Verteilung der Flüchtlinge in Deutschland Bevölkerungszahl und Wirtschaftskraft eine Rolle spielen und nicht die Frage 'Wieviel Platz hat man so?
+'.
+Das haben wir aber gemeistert und haben uns auch über viele Standorte verständigt, haben mit vielen Bürgerinnen und Bürgern gesprochenen, verhandelt, haben unglaublich viel Unterstützung bekommen von denjenigen, die in den Flüchtlingsunterkünften helfen.
+Und wir haben sofort dafür gesorgt, dass mehr Angebote gemacht werden bei Krippen und Kitas, bei den Schulen, haben zusätzliche Lehrerinnen und Lehrer eingestellt, damit es ohne Beeinträchtigung des bisherigen Betriebs zu einer schnellen Integration der jungen Leute kommt.
+Wir haben uns sofort darauf konzentriert, diejenigen, die in dem Alter sind, in dem man zur Berufsschule geht, dort auszubilden, auch mit einer Berufsorientierung zu versehen.
+Und wir haben Angebote entwickelt, die für diejenigen, die erwachsen sind, eine Arbeitsmarktintegration in den Blick nehmen.
+Detjen: Und vieles ist noch zu tun.
+Würden Sie Ihren Bürgerinnen und Bürgern in Hamburg sagen:  Wir schaffen das ?
+Scholz: Wer realistisch ist, kann immer nur sagen: Wir können das schaffen.
+Aber die Bürgerinnen und Bürger haben einen großen Beitrag dazu geleistet, dass zusammen mit einer sehr engagierten Verwaltung wir ganz schön weit gekommen sind und uns jetzt an die nächsten Aufgaben machen.
+Detjen: Herr Bürgermeister, vielen Dank.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Detjen: Das bezieht sich jetzt auf Koalitionen 
+Ist das für Sie erstrebenswert?
+Und das sollte auch im Vordergrund der Bemühungen stehen.
+Ich fände es auch sehr gut möglich, Das glaube ich schon.
+Detjen: Das war in Nordrhein-Westfalen offenbar nicht so einfach.
+Was ist da schiefgelaufen?
+Ich glaube, dass alle sehr betrübt darüber sind, dass es so ist.
+Der Vorsitzende des SPD-Unterbezirks Essen, der nordrhein-westfälische Justizminister </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -793,7 +788,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="364" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +807,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="350" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -822,6 +817,25 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C22CB57-2B64-47C4-8A57-D40962722177}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="30.9140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="252" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -835,27 +849,27 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
@@ -864,7 +878,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/new/260830.xlsx
+++ b/new/260830.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6A0B4FF-5093-4775-9A1B-9D408ED966B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8400" yWindow="4110" windowWidth="15030" windowHeight="11170" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8400" yWindow="4110" windowWidth="15030" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
